--- a/topics covered.xlsx
+++ b/topics covered.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">basics </t>
   </si>
@@ -39,6 +39,18 @@
   </si>
   <si>
     <t>require()</t>
+  </si>
+  <si>
+    <t>importing</t>
+  </si>
+  <si>
+    <t>exporting modules</t>
+  </si>
+  <si>
+    <t>fs.readFileSync()</t>
+  </si>
+  <si>
+    <t>fs.writeFileSync()</t>
   </si>
 </sst>
 </file>
@@ -368,6 +380,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="3:5" x14ac:dyDescent="0.35">
@@ -375,30 +388,40 @@
         <v>46199</v>
       </c>
       <c r="D5" s="1">
-        <v>46200</v>
-      </c>
-      <c r="E5" s="1">
-        <v>46201</v>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>0</v>
       </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>1</v>
       </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>4</v>
       </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.35">

--- a/topics covered.xlsx
+++ b/topics covered.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">basics </t>
   </si>
@@ -51,6 +51,33 @@
   </si>
   <si>
     <t>fs.writeFileSync()</t>
+  </si>
+  <si>
+    <t>nodemon installed</t>
+  </si>
+  <si>
+    <t>script added for start</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>1- syntax error</t>
+  </si>
+  <si>
+    <t>2- logical error</t>
+  </si>
+  <si>
+    <t>3- runtime error</t>
+  </si>
+  <si>
+    <t>debugging</t>
+  </si>
+  <si>
+    <t>express js</t>
+  </si>
+  <si>
+    <t>thunderclient</t>
   </si>
 </sst>
 </file>
@@ -60,7 +87,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="B1dd\-mmm\-yy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,16 +96,30 @@
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -86,18 +127,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Check Cell" xfId="1" builtinId="23"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -376,58 +439,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C5:E10"/>
+  <dimension ref="C4:F16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C5" s="2">
+    <row r="4" spans="3:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="3:6" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="1">
         <v>46199</v>
       </c>
       <c r="D5" s="1">
         <v>46206</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C6" t="s">
+      <c r="E5" s="1">
+        <v>46208</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C7" t="s">
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C9" t="s">
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C10" t="s">
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
